--- a/data/trans_bre/P6906-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P6906-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 21,39</t>
+          <t>-12,51; 20,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 32,48</t>
+          <t>-3,67; 35,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,4; 28,45</t>
+          <t>-13,73; 27,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,62; 19,55</t>
+          <t>-10,02; 18,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-65,04; 207,24</t>
+          <t>-69,94; 223,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,9; 269,48</t>
+          <t>-16,47; 281,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-47,94; 196,73</t>
+          <t>-48,97; 187,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-40,68; 209,25</t>
+          <t>-39,79; 174,71</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-16,98; 7,34</t>
+          <t>-16,41; 7,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 27,38</t>
+          <t>-5,62; 25,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 32,64</t>
+          <t>3,14; 32,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 20,58</t>
+          <t>-2,98; 19,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-67,05; 41,95</t>
+          <t>-66,67; 44,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,62; 152,73</t>
+          <t>-19,45; 141,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 306,11</t>
+          <t>10,37; 330,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 179,62</t>
+          <t>-18,18; 175,76</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 23,86</t>
+          <t>-7,74; 24,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-31,58; 0,84</t>
+          <t>-31,18; 0,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,19; 15,42</t>
+          <t>-12,52; 15,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,71; 16,93</t>
+          <t>-18,88; 16,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-33,75; 160,5</t>
+          <t>-30,58; 161,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-71,16; 5,97</t>
+          <t>-71,62; 5,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-41,63; 76,36</t>
+          <t>-41,91; 73,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-65,49; 148,46</t>
+          <t>-67,73; 135,31</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,12; 6,68</t>
+          <t>-16,22; 6,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 21,78</t>
+          <t>-8,21; 21,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 25,29</t>
+          <t>-6,82; 25,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 20,52</t>
+          <t>-3,06; 20,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,7; 28,62</t>
+          <t>-49,33; 25,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,41; 114,68</t>
+          <t>-27,32; 118,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-20,01; 118,2</t>
+          <t>-20,8; 116,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,41; 132,31</t>
+          <t>-10,39; 123,11</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 5,66</t>
+          <t>-7,47; 6,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 12,51</t>
+          <t>-4,43; 12,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 17,14</t>
+          <t>0,83; 16,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 12,86</t>
+          <t>-2,77; 12,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-29,87; 28,61</t>
+          <t>-29,74; 33,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,34; 54,22</t>
+          <t>-14,58; 53,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 81,76</t>
+          <t>2,24; 80,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 82,42</t>
+          <t>-11,65; 80,99</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P6906-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P6906-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,6</t>
+          <t>3,99</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>20,24%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,51; 20,77</t>
+          <t>-11,22; 21,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 35,81</t>
+          <t>-2,74; 34,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 27,21</t>
+          <t>-12,49; 30,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 18,64</t>
+          <t>-13,82; 16,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-69,94; 223,79</t>
+          <t>-60,07; 259,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,47; 281,2</t>
+          <t>-16,59; 262,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-48,97; 187,05</t>
+          <t>-42,12; 212,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-39,79; 174,71</t>
+          <t>-46,78; 157,2</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,69</t>
+          <t>6,78</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>35,21%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-16,41; 7,36</t>
+          <t>-17,31; 6,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 25,76</t>
+          <t>-5,7; 26,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,14; 32,94</t>
+          <t>1,32; 32,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 19,0</t>
+          <t>-4,38; 18,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-66,67; 44,89</t>
+          <t>-67,99; 36,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,45; 141,87</t>
+          <t>-19,05; 144,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,37; 330,01</t>
+          <t>-1,12; 283,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-18,18; 175,76</t>
+          <t>-17,65; 138,73</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,03</t>
+          <t>9,27</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>51,73%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 24,64</t>
+          <t>-7,04; 23,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-31,18; 0,91</t>
+          <t>-30,6; 0,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,52; 15,46</t>
+          <t>-12,5; 15,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,88; 16,79</t>
+          <t>-5,51; 23,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-30,58; 161,44</t>
+          <t>-31,24; 157,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-71,62; 5,39</t>
+          <t>-72,17; 5,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-41,91; 73,5</t>
+          <t>-42,68; 76,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-67,73; 135,31</t>
+          <t>-24,76; 228,76</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,14</t>
+          <t>9,46</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>41,4%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,22; 6,08</t>
+          <t>-17,2; 5,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 21,56</t>
+          <t>-10,24; 20,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 25,02</t>
+          <t>-6,35; 25,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 20,12</t>
+          <t>-2,29; 20,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,33; 25,86</t>
+          <t>-50,43; 27,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-27,32; 118,18</t>
+          <t>-35,29; 107,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-20,8; 116,29</t>
+          <t>-19,2; 114,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 123,11</t>
+          <t>-7,82; 131,34</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,2</t>
+          <t>7,7</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>38,3%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 6,84</t>
+          <t>-7,67; 5,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 12,31</t>
+          <t>-4,49; 11,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 16,8</t>
+          <t>0,82; 16,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 12,5</t>
+          <t>1,0; 14,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-29,74; 33,56</t>
+          <t>-31,36; 29,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,58; 53,88</t>
+          <t>-16,32; 45,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,24; 80,58</t>
+          <t>2,56; 82,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 80,99</t>
+          <t>4,37; 86,71</t>
         </is>
       </c>
     </row>
